--- a/data/trans_orig/P16A_n_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16A_n_R-Clase-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según número de medicamentos consumidos por persona en las dos últimas semanas</t>
+          <t>Población según número de medicamentos consumidos por persona en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -721,47 +721,47 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,15</t>
+          <t>0,79; 1,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 1,05</t>
+          <t>0,79; 1,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,24</t>
+          <t>1,01; 1,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,08</t>
+          <t>0,81; 1,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 1,28</t>
+          <t>0,94; 1,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,03</t>
+          <t>0,79; 1,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 1,4</t>
+          <t>1,12; 1,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 0,91</t>
+          <t>0,73; 0,9</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 1,15</t>
+          <t>0,89; 1,13</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -861,37 +861,37 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,03</t>
+          <t>0,78; 1,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 0,97</t>
+          <t>0,74; 0,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 1,31</t>
+          <t>1,03; 1,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 1,04</t>
+          <t>0,79; 1,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,32</t>
+          <t>1,01; 1,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,15</t>
+          <t>0,86; 1,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 1,41</t>
+          <t>1,16; 1,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 1,01</t>
+          <t>0,84; 1,02</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 1,32</t>
+          <t>1,12; 1,31</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 0,8</t>
+          <t>0,6; 0,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 1,37</t>
+          <t>1,07; 1,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1011,47 +1011,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,57</t>
+          <t>0,37; 1,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 1,45</t>
+          <t>0,96; 1,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 1,7</t>
+          <t>1,3; 1,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 1,94</t>
+          <t>1,37; 1,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 2,5</t>
+          <t>1,97; 2,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 0,92</t>
+          <t>0,72; 0,93</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,18; 1,42</t>
+          <t>1,16; 1,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 1,26</t>
+          <t>1,04; 1,25</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,76</t>
+          <t>0,58; 1,75</t>
         </is>
       </c>
     </row>
@@ -1136,32 +1136,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 0,92</t>
+          <t>0,78; 0,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,22</t>
+          <t>1,05; 1,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 1,08</t>
+          <t>0,93; 1,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,3; 1,52</t>
+          <t>1,29; 1,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,94; 1,13</t>
+          <t>0,93; 1,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,27; 1,49</t>
+          <t>1,25; 1,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,49; 2,97</t>
+          <t>1,49; 2,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 0,98</t>
+          <t>0,85; 0,97</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,43; 2,35</t>
+          <t>1,44; 2,46</t>
         </is>
       </c>
     </row>
@@ -1276,57 +1276,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 0,92</t>
+          <t>0,63; 0,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 1,16</t>
+          <t>0,92; 1,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,94; 1,17</t>
+          <t>0,93; 1,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,19; 1,5</t>
+          <t>1,18; 1,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,25</t>
+          <t>1,03; 1,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,75; 2,05</t>
+          <t>1,76; 2,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,52; 1,78</t>
+          <t>1,54; 1,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,75; 2,3</t>
+          <t>1,78; 2,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 1,08</t>
+          <t>0,91; 1,09</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 1,66</t>
+          <t>1,45; 1,67</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,28; 1,46</t>
+          <t>1,29; 1,46</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1421,47 +1421,47 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,52</t>
+          <t>0,32; 0,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,46</t>
+          <t>0,27; 0,45</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,69</t>
+          <t>0,32; 0,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,25; 1,41</t>
+          <t>1,24; 1,41</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,81; 2,06</t>
+          <t>1,83; 2,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,57; 1,79</t>
+          <t>1,57; 1,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,82; 2,12</t>
+          <t>1,83; 2,13</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,05; 1,19</t>
+          <t>1,04; 1,19</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,53; 1,75</t>
+          <t>1,54; 1,75</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,48; 1,74</t>
+          <t>1,48; 1,75</t>
         </is>
       </c>
     </row>
@@ -1561,17 +1561,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,96; 1,07</t>
+          <t>0,97; 1,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,88; 0,96</t>
+          <t>0,88; 0,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,27</t>
+          <t>0,92; 1,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1581,37 +1581,37 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,56; 1,68</t>
+          <t>1,57; 1,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,34; 1,45</t>
+          <t>1,35; 1,45</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,72; 2,29</t>
+          <t>1,72; 2,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,9; 0,97</t>
+          <t>0,9; 0,96</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,28; 1,37</t>
+          <t>1,29; 1,37</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,12; 1,2</t>
+          <t>1,13; 1,2</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,38; 1,74</t>
+          <t>1,38; 1,75</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A_n_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16A_n_R-Clase-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,11</t>
+          <t>1,1</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,18</t>
+          <t>1,17</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,16</t>
+          <t>0,79; 1,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,05</t>
+          <t>0,8; 1,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 1,24</t>
+          <t>0,99; 1,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -741,17 +741,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 1,28</t>
+          <t>0,95; 1,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,02</t>
+          <t>0,78; 1,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 1,39</t>
+          <t>1,13; 1,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,16</t>
+          <t>1,14</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,29</t>
+          <t>1,28</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,22</t>
+          <t>1,21</t>
         </is>
       </c>
     </row>
@@ -856,27 +856,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 0,74</t>
+          <t>0,51; 0,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 1,05</t>
+          <t>0,77; 1,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 0,96</t>
+          <t>0,74; 0,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,03; 1,3</t>
+          <t>1,01; 1,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,03</t>
+          <t>0,8; 1,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -886,27 +886,27 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,14</t>
+          <t>0,85; 1,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,16; 1,43</t>
+          <t>1,15; 1,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 0,84</t>
+          <t>0,68; 0,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 1,12</t>
+          <t>0,91; 1,11</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 1,02</t>
+          <t>0,83; 1,0</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,96</t>
+          <t>1,46</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,21</t>
+          <t>2,19</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,21</t>
+          <t>1,67</t>
         </is>
       </c>
     </row>
@@ -996,27 +996,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 0,8</t>
+          <t>0,62; 0,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 1,35</t>
+          <t>1,07; 1,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 1,1</t>
+          <t>0,89; 1,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,59</t>
+          <t>1,3; 1,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 1,44</t>
+          <t>0,94; 1,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1026,22 +1026,22 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 1,93</t>
+          <t>1,35; 1,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 2,53</t>
+          <t>1,92; 2,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 0,93</t>
+          <t>0,73; 0,91</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 1,41</t>
+          <t>1,18; 1,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,75</t>
+          <t>1,53; 1,84</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,4</t>
+          <t>1,39</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,05</t>
+          <t>1,53</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,71</t>
+          <t>1,45</t>
         </is>
       </c>
     </row>
@@ -1136,47 +1136,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 0,93</t>
+          <t>0,78; 0,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 1,23</t>
+          <t>1,04; 1,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 1,09</t>
+          <t>0,92; 1,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 1,52</t>
+          <t>1,28; 1,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 1,14</t>
+          <t>0,94; 1,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 1,48</t>
+          <t>1,26; 1,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 1,25</t>
+          <t>1,04; 1,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,49; 2,83</t>
+          <t>1,43; 1,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 0,97</t>
+          <t>0,86; 0,98</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,44; 2,46</t>
+          <t>1,37; 1,52</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,33</t>
+          <t>1,22</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,09</t>
+          <t>2,2</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,82</t>
+          <t>1,8</t>
         </is>
       </c>
     </row>
@@ -1276,22 +1276,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 0,91</t>
+          <t>0,64; 0,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,92; 1,17</t>
+          <t>0,91; 1,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 1,15</t>
+          <t>0,94; 1,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,18; 1,48</t>
+          <t>1,09; 1,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1306,12 +1306,12 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,54; 1,79</t>
+          <t>1,53; 1,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,78; 2,33</t>
+          <t>2,08; 2,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1321,24 +1321,24 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,45; 1,67</t>
+          <t>1,45; 1,66</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,29; 1,46</t>
+          <t>1,29; 1,45</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,63; 1,96</t>
+          <t>1,71; 1,91</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1,98</t>
+          <t>1,95</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,61</t>
+          <t>1,62</t>
         </is>
       </c>
     </row>
@@ -1421,17 +1421,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,53</t>
+          <t>0,32; 0,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,45</t>
+          <t>0,27; 0,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,67</t>
+          <t>0,31; 0,66</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,83; 2,07</t>
+          <t>1,82; 2,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,83; 2,13</t>
+          <t>1,82; 2,09</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,54; 1,75</t>
+          <t>1,53; 1,75</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,31; 1,5</t>
+          <t>1,31; 1,51</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,48; 1,75</t>
+          <t>1,49; 1,75</t>
         </is>
       </c>
     </row>
@@ -1503,47 +1503,47 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
+          <t>1,23</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,14</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,62</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1,75</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0,93</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1,32</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
           <t>1,16</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,14</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,62</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,4</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1,87</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0,93</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1,32</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>1,16</t>
-        </is>
-      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,52</t>
+          <t>1,49</t>
         </is>
       </c>
     </row>
@@ -1566,17 +1566,17 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,88; 0,97</t>
+          <t>0,87; 0,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,92; 1,27</t>
+          <t>1,17; 1,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,09; 1,19</t>
+          <t>1,1; 1,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1586,12 +1586,12 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,35; 1,45</t>
+          <t>1,34; 1,45</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,72; 2,28</t>
+          <t>1,69; 1,8</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,29; 1,37</t>
+          <t>1,28; 1,37</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,38; 1,75</t>
+          <t>1,45; 1,54</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A_n_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16A_n_R-Clase-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según número de medicamentos consumidos por persona en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
+          <t>Población según el número de medicamentos consumidos por persona en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
